--- a/artfynd/S 316-2024 artfynd.xlsx
+++ b/artfynd/S 316-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ20"/>
+  <dimension ref="A1:AZ21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1235,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>77768070</v>
+        <v>137112054</v>
       </c>
       <c r="B7" t="n">
-        <v>57132</v>
+        <v>57195</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1246,42 +1246,56 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>102612</v>
+        <v>100138</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>O Lomflytjärnen, Vstm</t>
+          <t>Lomflytjärnen, Vstm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>488039</v>
+        <v>487789</v>
       </c>
       <c r="R7" t="n">
-        <v>6603650</v>
+        <v>6603508</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1305,17 +1319,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2019-04-27</t>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2019-04-27</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Spillningshög i kärrkant, gulbruna lortar 1,5-2 x 0,5 cm</t>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1330,27 +1349,27 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kaj Svahn</t>
+          <t>Nils Nygren</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Tony Svensson</t>
+          <t>Nils Nygren</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/77768070</t>
+          <t>https://artportalen.se/Sighting/137112054</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>77768953</v>
+        <v>77768070</v>
       </c>
       <c r="B8" t="n">
-        <v>57144</v>
+        <v>57132</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1358,16 +1377,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>102613</v>
+        <v>102612</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1375,26 +1394,22 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>hona</t>
+      <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>O Klampmossen, Vstm</t>
+          <t>O Lomflytjärnen, Vstm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>487739</v>
+        <v>488039</v>
       </c>
       <c r="R8" t="n">
-        <v>6604036</v>
+        <v>6603650</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1421,12 +1436,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2019-04-28</t>
+          <t>2019-04-27</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2019-04-28</t>
+          <t>2019-04-27</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Spillningshög i kärrkant, gulbruna lortar 1,5-2 x 0,5 cm</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1446,22 +1466,22 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kaj Svahn</t>
+          <t>Tony Svensson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/77768953</t>
+          <t>https://artportalen.se/Sighting/77768070</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>78129137</v>
+        <v>77768953</v>
       </c>
       <c r="B9" t="n">
-        <v>97983</v>
+        <v>57144</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1469,34 +1489,43 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221945</v>
+        <v>102613</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Kultermossen, Vstm</t>
+          <t>O Klampmossen, Vstm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>488134</v>
+        <v>487739</v>
       </c>
       <c r="R9" t="n">
-        <v>6603809</v>
+        <v>6604036</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1523,12 +1552,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2019-05-08</t>
+          <t>2019-04-28</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2019-05-08</t>
+          <t>2019-04-28</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1543,27 +1572,27 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kaj Svahn</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kaj Svahn</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/78129137</t>
+          <t>https://artportalen.se/Sighting/77768953</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>77768043</v>
+        <v>78129137</v>
       </c>
       <c r="B10" t="n">
-        <v>97986</v>
+        <v>97983</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1571,16 +1600,16 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221946</v>
+        <v>221945</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1591,14 +1620,14 @@
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>NO Lomflytjärnen, Vstm</t>
+          <t>Kultermossen, Vstm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>487801</v>
+        <v>488134</v>
       </c>
       <c r="R10" t="n">
-        <v>6603672</v>
+        <v>6603809</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1625,17 +1654,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2019-04-27</t>
+          <t>2019-05-08</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2019-04-27</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ganska tätt i vägkant</t>
+          <t>2019-05-08</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1650,24 +1674,24 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kaj Svahn</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Sofia Lund</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/77768043</t>
+          <t>https://artportalen.se/Sighting/78129137</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>77768045</v>
+        <v>77768043</v>
       </c>
       <c r="B11" t="n">
         <v>97986</v>
@@ -1698,14 +1722,14 @@
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>O Klampmossen, Vstm</t>
+          <t>NO Lomflytjärnen, Vstm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>487834</v>
+        <v>487801</v>
       </c>
       <c r="R11" t="n">
-        <v>6604177</v>
+        <v>6603672</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1742,7 +1766,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Spridd i vägkanten</t>
+          <t>Ganska tätt i vägkant</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1768,16 +1792,16 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/77768045</t>
+          <t>https://artportalen.se/Sighting/77768043</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>77640658</v>
+        <v>77768045</v>
       </c>
       <c r="B12" t="n">
-        <v>97983</v>
+        <v>97986</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1785,16 +1809,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221945</v>
+        <v>221946</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1803,20 +1827,16 @@
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Kraftledningsgata V Kultermossen, Vstm</t>
+          <t>O Klampmossen, Vstm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>488962</v>
+        <v>487834</v>
       </c>
       <c r="R12" t="n">
-        <v>6603172</v>
+        <v>6604177</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1843,12 +1863,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2019-05-08</t>
+          <t>2019-04-27</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2019-05-08</t>
+          <t>2019-04-27</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Spridd i vägkanten</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1857,14 +1882,13 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Sofia Lund</t>
+          <t>Kaj Svahn</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
@@ -1875,16 +1899,16 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/77640658</t>
+          <t>https://artportalen.se/Sighting/77768045</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>77640660</v>
+        <v>77640658</v>
       </c>
       <c r="B13" t="n">
-        <v>97986</v>
+        <v>97983</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1892,16 +1916,16 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221946</v>
+        <v>221945</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1982,58 +2006,58 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/77640660</t>
+          <t>https://artportalen.se/Sighting/77640658</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>7121567</v>
+        <v>77640660</v>
       </c>
       <c r="B14" t="n">
-        <v>79327</v>
+        <v>97986</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>221946</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Rockesholm, Vstm</t>
+          <t>Kraftledningsgata V Kultermossen, Vstm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>480720</v>
+        <v>488962</v>
       </c>
       <c r="R14" t="n">
-        <v>6601587</v>
+        <v>6603172</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2057,17 +2081,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2011-08-16</t>
+          <t>2019-05-08</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2011-08-16</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Sveaskogs Naturvärdesinventering -Inventerare: Emil P A  ID;29955</t>
+          <t>2019-05-08</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2076,55 +2095,56 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Sveaskog genom Johan Ekenstedt</t>
+          <t>Sofia Lund</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Sveaskog genom Johan Ekenstedt</t>
+          <t>Sofia Lund</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/7121567</t>
+          <t>https://artportalen.se/Sighting/77640660</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>79933722</v>
+        <v>7121567</v>
       </c>
       <c r="B15" t="n">
-        <v>28299</v>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>102628</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Korthornad vedstekel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tremex fuscicornis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fabricius, 1787)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2132,32 +2152,19 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Öster om Rockersholm, Vstm</t>
+          <t>Rockesholm, Vstm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>480308</v>
+        <v>480720</v>
       </c>
       <c r="R15" t="n">
-        <v>6600135</v>
+        <v>6601587</v>
       </c>
       <c r="S15" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2181,22 +2188,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2019-09-15</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>17:00</t>
+          <t>2011-08-16</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2019-09-15</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>17:00</t>
+          <t>2011-08-16</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Sveaskogs Naturvärdesinventering -Inventerare: Emil P A  ID;29955</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2205,49 +2207,33 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>vårtbjörk</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Betula pendula</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Betula pendula</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Anders Carlberg</t>
+          <t>Sveaskog genom Johan Ekenstedt</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Anders Carlberg, Camilla Pettersson</t>
+          <t>Sveaskog genom Johan Ekenstedt</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/79933722</t>
+          <t>https://artportalen.se/Sighting/7121567</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>81276301</v>
+        <v>79933722</v>
       </c>
       <c r="B16" t="n">
-        <v>87343</v>
+        <v>28299</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2255,37 +2241,54 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>464</v>
+        <v>102628</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gulnande spindling</t>
+          <t>Korthornad vedstekel</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cortinarius rubicundulus</t>
+          <t>Tremex fuscicornis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Rea) A.Pearson</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(Fabricius, 1787)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Sågforsudden, Vstm</t>
+          <t>Öster om Rockersholm, Vstm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>484622</v>
+        <v>480308</v>
       </c>
       <c r="R16" t="n">
-        <v>6598205</v>
+        <v>6600135</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2309,12 +2312,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2019-08-30</t>
+          <t>2019-09-15</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2019-11-30</t>
+          <t>2019-09-15</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2323,55 +2336,71 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>vårtbjörk</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Betula pendula</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Betula pendula</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Anders Carlberg</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Anders Carlberg, Camilla Pettersson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/81276301</t>
+          <t>https://artportalen.se/Sighting/79933722</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>81276279</v>
+        <v>81276301</v>
       </c>
       <c r="B17" t="n">
-        <v>93189</v>
+        <v>87343</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4361</v>
+        <v>464</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Gulnande spindling</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Cortinarius rubicundulus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Rea) A.Pearson</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2384,7 +2413,7 @@
         <v>484622</v>
       </c>
       <c r="R17" t="n">
-        <v>6598210</v>
+        <v>6598205</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2442,38 +2471,38 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/81276279</t>
+          <t>https://artportalen.se/Sighting/81276301</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>81276276</v>
+        <v>81276279</v>
       </c>
       <c r="B18" t="n">
-        <v>97983</v>
+        <v>93189</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221945</v>
+        <v>4361</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2483,10 +2512,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>484592</v>
+        <v>484622</v>
       </c>
       <c r="R18" t="n">
-        <v>6598369</v>
+        <v>6598210</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2544,16 +2573,16 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/81276276</t>
+          <t>https://artportalen.se/Sighting/81276279</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>81276290</v>
+        <v>81276276</v>
       </c>
       <c r="B19" t="n">
-        <v>99038</v>
+        <v>97983</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2561,19 +2590,23 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>223597</v>
+        <v>221945</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr"/>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2581,10 +2614,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>484615</v>
+        <v>484592</v>
       </c>
       <c r="R19" t="n">
-        <v>6598193</v>
+        <v>6598369</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2642,13 +2675,13 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/81276290</t>
+          <t>https://artportalen.se/Sighting/81276276</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>81276291</v>
+        <v>81276290</v>
       </c>
       <c r="B20" t="n">
         <v>99038</v>
@@ -2679,10 +2712,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>484673</v>
+        <v>484615</v>
       </c>
       <c r="R20" t="n">
-        <v>6598396</v>
+        <v>6598193</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2739,6 +2772,104 @@
       </c>
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81276290</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>81276291</v>
+      </c>
+      <c r="B21" t="n">
+        <v>99038</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>223597</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Jungfru marie nycklar</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Sågforsudden, Vstm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>484673</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6598396</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2019-08-30</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2019-11-30</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/81276291</t>
         </is>
@@ -2765,6 +2896,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/S 316-2024 artfynd.xlsx
+++ b/artfynd/S 316-2024 artfynd.xlsx
@@ -1238,7 +1238,7 @@
         <v>137112054</v>
       </c>
       <c r="B7" t="n">
-        <v>57195</v>
+        <v>57208</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/S 316-2024 artfynd.xlsx
+++ b/artfynd/S 316-2024 artfynd.xlsx
@@ -1238,7 +1238,7 @@
         <v>137112054</v>
       </c>
       <c r="B7" t="n">
-        <v>57208</v>
+        <v>57210</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/S 316-2024 artfynd.xlsx
+++ b/artfynd/S 316-2024 artfynd.xlsx
@@ -1268,21 +1268,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Lomflytjärnen, Vstm</t>

--- a/artfynd/S 316-2024 artfynd.xlsx
+++ b/artfynd/S 316-2024 artfynd.xlsx
@@ -1238,7 +1238,7 @@
         <v>137112054</v>
       </c>
       <c r="B7" t="n">
-        <v>57210</v>
+        <v>57220</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/S 316-2024 artfynd.xlsx
+++ b/artfynd/S 316-2024 artfynd.xlsx
@@ -1238,7 +1238,7 @@
         <v>137112054</v>
       </c>
       <c r="B7" t="n">
-        <v>57220</v>
+        <v>57221</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/S 316-2024 artfynd.xlsx
+++ b/artfynd/S 316-2024 artfynd.xlsx
@@ -1238,7 +1238,7 @@
         <v>137112054</v>
       </c>
       <c r="B7" t="n">
-        <v>57221</v>
+        <v>57224</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
